--- a/docs/04_품질보안점검.xlsx
+++ b/docs/04_품질보안점검.xlsx
@@ -103,7 +103,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -125,11 +125,55 @@
         <color rgb="00CFE3F0"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CFE3F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CFE3F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CFE3F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CFE3F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CFE3F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CFE3F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CFE3F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CFE3F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -161,6 +205,8 @@
     <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -526,7 +572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -555,6 +601,10 @@
           <t>상용 출시 기준 품질·보안 점검·추적표</t>
         </is>
       </c>
+      <c r="C2" s="11" t="n"/>
+      <c r="D2" s="11" t="n"/>
+      <c r="E2" s="11" t="n"/>
+      <c r="F2" s="12" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -564,9 +614,13 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>v1</t>
-        </is>
-      </c>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="n"/>
+      <c r="D3" s="11" t="n"/>
+      <c r="E3" s="11" t="n"/>
+      <c r="F3" s="12" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -579,6 +633,10 @@
           <t>2026-06-30</t>
         </is>
       </c>
+      <c r="C4" s="11" t="n"/>
+      <c r="D4" s="11" t="n"/>
+      <c r="E4" s="11" t="n"/>
+      <c r="F4" s="12" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -591,6 +649,10 @@
           <t>P0 출시 전 필수 / P1 베타 전 / P2 정식 런칭</t>
         </is>
       </c>
+      <c r="C5" s="11" t="n"/>
+      <c r="D5" s="11" t="n"/>
+      <c r="E5" s="11" t="n"/>
+      <c r="F5" s="12" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -603,6 +665,10 @@
           <t>✅ 완료 / 🔧 진행중 / ⬜ 예정</t>
         </is>
       </c>
+      <c r="C6" s="11" t="n"/>
+      <c r="D6" s="11" t="n"/>
+      <c r="E6" s="11" t="n"/>
+      <c r="F6" s="12" t="n"/>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
@@ -1081,6 +1147,38 @@
       <c r="F21" s="8" t="inlineStr">
         <is>
           <t>localStorage 토큰 — 무효화·XSS 강화는 추후</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>SEC-11</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>인증</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>추천 API 무인증 호출(비용 어뷰징)</t>
+        </is>
+      </c>
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>Vercel 함수(/api/outfit·/api/shop)에 JWT 검증 + 계정별 일일 상한(outfit 50회/shop 600회). 프론트는 로그인 토큰 첨부. Vercel env에 JWT_SECRET 필요</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1202,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1199,6 +1297,18 @@
       <c r="B8" s="8" t="inlineStr">
         <is>
           <t>날씨 격자 캐시·추천 결과 캐시로 호출 한도/지연 완화</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>추천 API 보호</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>JWT 검증 + 계정별 일일 호출 상한(비용 어뷰징 차단)</t>
         </is>
       </c>
     </row>
@@ -1217,7 +1327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1266,6 +1376,23 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>SEC-11 추가 — 추천 API JWT 검증+계정별 일일 상한 적용(완료)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A2:C2"/>
   <mergeCells count="1">

--- a/docs/04_품질보안점검.xlsx
+++ b/docs/04_품질보안점검.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>v2</t>
+          <t>v4</t>
         </is>
       </c>
       <c r="C3" s="11" t="n"/>
@@ -1013,12 +1013,12 @@
       </c>
       <c r="E17" s="10" t="inlineStr">
         <is>
-          <t>예정</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="F17" s="8" t="inlineStr">
         <is>
-          <t>이메일 발송 인프라는 구축됨 → 재설정 토큰 흐름 추가 예정</t>
+          <t>이메일 재설정 흐름 구현 — /auth/forgot(존재여부 비노출)→메일 링크 폼→/auth/reset(1시간·1회용 토큰). 회원 탈퇴(DELETE /auth/account, 비밀번호 재확인)도 함께</t>
         </is>
       </c>
     </row>
@@ -1045,12 +1045,12 @@
       </c>
       <c r="E18" s="10" t="inlineStr">
         <is>
-          <t>예정</t>
+          <t>진행중</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>단일 VM SQLite — cron으로 DB 파일 일 단위 복사 예정</t>
+          <t>VM 내 일일 자동 백업 구축(cron 04:00 KST, sqlite3 .backup — WAL 포함, gzip, 14일 보관, 복원 검증 완료). 남은 것: OCI Object Storage PAR 등록 시 오프서버 업로드(스크립트 준비됨)</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1393,6 +1393,40 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>OPS-01 갱신 — VM 내 일일 DB 백업 구축(예정→진행중), 오프서버 업로드만 잔여</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>v4</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>SEC-09 완료 — 비밀번호 재설정 + 회원 탈퇴 구현</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A2:C2"/>
   <mergeCells count="1">

--- a/docs/04_품질보안점검.xlsx
+++ b/docs/04_품질보안점검.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>v4</t>
+          <t>v5</t>
         </is>
       </c>
       <c r="C3" s="11" t="n"/>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t>수집·보관·파기 고지(이메일·이름 수집)</t>
+          <t>수집·보관·파기 고지(이메일·이름 수집) · 옷 사진은 AI 분석을 위해 외부(Claude API)로 전송 — 방침에 고지 필요</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="F22" s="8" t="inlineStr">
         <is>
-          <t>Vercel 함수(/api/outfit·/api/shop)에 JWT 검증 + 계정별 일일 상한(outfit 50회/shop 600회). 프론트는 로그인 토큰 첨부. Vercel env에 JWT_SECRET 필요</t>
+          <t>Vercel 함수(/api/outfit·/api/shop·/api/vision)에 JWT 검증 + 계정별 일일 상한(outfit 50회/shop 600회). 프론트는 로그인 토큰 첨부. Vercel env에 JWT_SECRET 필요</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1427,6 +1427,23 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>v5</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>사진 옷 등록 반영 — SEC-11 보호 범위에 /api/vision 포함, LEG-01에 옷 사진 외부 전송 고지 필요 추가</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A2:C2"/>
   <mergeCells count="1">

--- a/docs/04_품질보안점검.xlsx
+++ b/docs/04_품질보안점검.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>v5</t>
+          <t>v6</t>
         </is>
       </c>
       <c r="C3" s="11" t="n"/>
@@ -1045,12 +1045,12 @@
       </c>
       <c r="E18" s="10" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>VM 내 일일 자동 백업 구축(cron 04:00 KST, sqlite3 .backup — WAL 포함, gzip, 14일 보관, 복원 검증 완료). 남은 것: OCI Object Storage PAR 등록 시 오프서버 업로드(스크립트 준비됨)</t>
+          <t>VM 내 일일 백업(cron 04:00 KST, 14일 보관) + OCI Object Storage 오프서버 업로드(쓰기 전용 PAR, weatherwear-backup 버킷, 업로드 검증 완료 2026-07-02)</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1444,6 +1444,23 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>v6</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>OPS-01 완료 — 오프서버 백업 사본(OCI Object Storage PAR) 활성화·업로드 검증</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A2:C2"/>
   <mergeCells count="1">
